--- a/egg_data.xlsx
+++ b/egg_data.xlsx
@@ -1,40 +1,747 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+  <si>
+    <t>精灵名称</t>
+  </si>
+  <si>
+    <t>尺寸最小</t>
+  </si>
+  <si>
+    <t>尺寸最大</t>
+  </si>
+  <si>
+    <t>重量最小</t>
+  </si>
+  <si>
+    <t>重量最大</t>
+  </si>
+  <si>
+    <t>旋叶虫</t>
+  </si>
+  <si>
+    <t>刺轮砣</t>
+  </si>
+  <si>
+    <t>画精灵</t>
+  </si>
+  <si>
+    <t>小鹬</t>
+  </si>
+  <si>
+    <t>菇菇丁</t>
+  </si>
+  <si>
+    <t>号儿鱼</t>
+  </si>
+  <si>
+    <t>毛毛</t>
+  </si>
+  <si>
+    <t>波波螺</t>
+  </si>
+  <si>
+    <t>逗逗</t>
+  </si>
+  <si>
+    <t>书魔虫</t>
+  </si>
+  <si>
+    <t>矮脚爬爬</t>
+  </si>
+  <si>
+    <t>雪娃娃</t>
+  </si>
+  <si>
+    <t>棋棋</t>
+  </si>
+  <si>
+    <t>哭哭菇</t>
+  </si>
+  <si>
+    <t>螺旋帕帕</t>
+  </si>
+  <si>
+    <t>蒲公英</t>
+  </si>
+  <si>
+    <t>兽花蕾</t>
+  </si>
+  <si>
+    <t>闪电环</t>
+  </si>
+  <si>
+    <t>丢丢灵</t>
+  </si>
+  <si>
+    <t>小箱怪</t>
+  </si>
+  <si>
+    <t>小鼠獭</t>
+  </si>
+  <si>
+    <t>粉星仔</t>
+  </si>
+  <si>
+    <t>优优</t>
+  </si>
+  <si>
+    <t>石石</t>
+  </si>
+  <si>
+    <t>豆丁鱼</t>
+  </si>
+  <si>
+    <t>大耳帽兜</t>
+  </si>
+  <si>
+    <t>雪绒鸟</t>
+  </si>
+  <si>
+    <t>小灵菇</t>
+  </si>
+  <si>
+    <t>格兰种子</t>
+  </si>
+  <si>
+    <t>柴渣虫</t>
+  </si>
+  <si>
+    <t>可立鸡</t>
+  </si>
+  <si>
+    <t>甜田螺</t>
+  </si>
+  <si>
+    <t>小灵面</t>
+  </si>
+  <si>
+    <t>一窝蜂</t>
+  </si>
+  <si>
+    <t>彩蝶鲨</t>
+  </si>
+  <si>
+    <t>丢丢</t>
+  </si>
+  <si>
+    <t>奇丽草</t>
+  </si>
+  <si>
+    <t>小草虫</t>
+  </si>
+  <si>
+    <t>绿翼鸟</t>
+  </si>
+  <si>
+    <t>权杖 - 11</t>
+  </si>
+  <si>
+    <t>乌达</t>
+  </si>
+  <si>
+    <t>多多</t>
+  </si>
+  <si>
+    <t>小电企鹅</t>
+  </si>
+  <si>
+    <t>风铃鲨</t>
+  </si>
+  <si>
+    <t>布是石</t>
+  </si>
+  <si>
+    <t>公平鸽</t>
+  </si>
+  <si>
+    <t>伊贝儿</t>
+  </si>
+  <si>
+    <t>吸泥鸥</t>
+  </si>
+  <si>
+    <t>奔波鼠</t>
+  </si>
+  <si>
+    <t>仪使者</t>
+  </si>
+  <si>
+    <t>拉特</t>
+  </si>
+  <si>
+    <t>矿晶虫</t>
+  </si>
+  <si>
+    <t>地鼠</t>
+  </si>
+  <si>
+    <t>石肤蜥</t>
+  </si>
+  <si>
+    <t>草头鸭</t>
+  </si>
+  <si>
+    <t>厉毒小萝</t>
+  </si>
+  <si>
+    <t>呼呼</t>
+  </si>
+  <si>
+    <t>阿米樱</t>
+  </si>
+  <si>
+    <t>小黑猫</t>
+  </si>
+  <si>
+    <t>圆眼蜘蛛</t>
+  </si>
+  <si>
+    <t>乖乖鸫</t>
+  </si>
+  <si>
+    <t>梦游</t>
+  </si>
+  <si>
+    <t>双灯鱼</t>
+  </si>
+  <si>
+    <t>绿耳松鼠</t>
+  </si>
+  <si>
+    <t>小怂猫</t>
+  </si>
+  <si>
+    <t>翡翠水母</t>
+  </si>
+  <si>
+    <t>小夜</t>
+  </si>
+  <si>
+    <t>花怨鳗</t>
+  </si>
+  <si>
+    <t>小甲虫</t>
+  </si>
+  <si>
+    <t>海盗虫</t>
+  </si>
+  <si>
+    <t>蹦蹦种子</t>
+  </si>
+  <si>
+    <t>板板壳</t>
+  </si>
+  <si>
+    <t>灵狐</t>
+  </si>
+  <si>
+    <t>阿米亚特</t>
+  </si>
+  <si>
+    <t>喵喵</t>
+  </si>
+  <si>
+    <t>电咩咩</t>
+  </si>
+  <si>
+    <t>锥尾羊</t>
+  </si>
+  <si>
+    <t>治愈兔</t>
+  </si>
+  <si>
+    <t>呼呼猪</t>
+  </si>
+  <si>
+    <t>呆小路</t>
+  </si>
+  <si>
+    <t>护主犬</t>
+  </si>
+  <si>
+    <t>粉粉星</t>
+  </si>
+  <si>
+    <t>菊花梨</t>
+  </si>
+  <si>
+    <t>嘟嘟煲</t>
+  </si>
+  <si>
+    <t>幽影树</t>
+  </si>
+  <si>
+    <t>火尾瓦特</t>
+  </si>
+  <si>
+    <t>海豹战士</t>
+  </si>
+  <si>
+    <t>海枝枝</t>
+  </si>
+  <si>
+    <t>小帕尔</t>
+  </si>
+  <si>
+    <t>电动长颈鹿</t>
+  </si>
+  <si>
+    <t>多西</t>
+  </si>
+  <si>
+    <t>鸭吉吉</t>
+  </si>
+  <si>
+    <t>可爱猿</t>
+  </si>
+  <si>
+    <t>绿草精灵</t>
+  </si>
+  <si>
+    <t>伊雷龙</t>
+  </si>
+  <si>
+    <t>小狮鹫</t>
+  </si>
+  <si>
+    <t>白发懒人</t>
+  </si>
+  <si>
+    <t>大头骨龙</t>
+  </si>
+  <si>
+    <t>小星光</t>
+  </si>
+  <si>
+    <t>胆小鳗鱼</t>
+  </si>
+  <si>
+    <t>里拉鳐</t>
+  </si>
+  <si>
+    <t>圣剑侍从</t>
+  </si>
+  <si>
+    <t>古钟蛇</t>
+  </si>
+  <si>
+    <t>雪豆丁</t>
+  </si>
+  <si>
+    <t>锤头鹳</t>
+  </si>
+  <si>
+    <t>雪蛮人</t>
+  </si>
+  <si>
+    <t>小翼龙</t>
+  </si>
+  <si>
+    <t>小独角兽</t>
+  </si>
+  <si>
+    <t>火红尾</t>
+  </si>
+  <si>
+    <t>记忆石</t>
+  </si>
+  <si>
+    <t>恶魔狼</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +749,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,85 +1338,1921 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E112"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>精灵名称</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>尺寸最小</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>尺寸最大</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>重量最小</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>重量最大</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>示例精灵A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.057</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.554</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.353</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.415</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.447</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="n">
+      <c r="B7" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.426</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.14</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.14</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.14</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.153</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="n">
+      <c r="B12" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1.184</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.646</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3.223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4.053</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4.651</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.749</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1.064</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.812</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1.571</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="n">
+      <c r="B17" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.037</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1.559</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2.171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.847</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1.187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1.299</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2.196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2.479</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2.479</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2.492</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2.727</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3.714</v>
+      </c>
+      <c r="E23" s="1">
+        <v>4.398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1.171</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1.315</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="D25" s="1">
+        <v>21.471</v>
+      </c>
+      <c r="E25" s="1">
+        <v>29.809</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.434</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1.203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>示例精灵B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="B27" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2.937</v>
+      </c>
+      <c r="E27" s="1">
+        <v>4.029</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1.166</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1.793</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2.078</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2.078</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1.408</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.678</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D31" s="1">
+        <v>5.247</v>
+      </c>
+      <c r="E31" s="1">
+        <v>5.976</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2.022</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2.627</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3.457</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.036</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1.666</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="D36" s="1">
+        <v>5.585</v>
+      </c>
+      <c r="E36" s="1">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2.355</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2.355</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1.842</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2.145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.777</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.934</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1.304</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1.471</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D41" s="1">
+        <v>12.073</v>
+      </c>
+      <c r="E41" s="1">
+        <v>12.904</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2.361</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D43" s="1">
+        <v>5.21</v>
+      </c>
+      <c r="E43" s="1">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1.835</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2.017</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D45" s="1">
+        <v>6.01</v>
+      </c>
+      <c r="E45" s="1">
+        <v>6.204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D46" s="1">
+        <v>9.627</v>
+      </c>
+      <c r="E46" s="1">
+        <v>12.703</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1.213</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1.452</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1.603</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1.603</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3.365</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3.528</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2.126</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2.126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="D51" s="1">
+        <v>12.203</v>
+      </c>
+      <c r="E51" s="1">
+        <v>12.203</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3.107</v>
+      </c>
+      <c r="E52" s="1">
+        <v>3.434</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2.101</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2.156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.933</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D55" s="1">
+        <v>8.091</v>
+      </c>
+      <c r="E55" s="1">
+        <v>11.642</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C56" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1.902</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2.336</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3.374</v>
+      </c>
+      <c r="E57" s="1">
+        <v>5.927</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2.417</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3.133</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D59" s="1">
+        <v>14.618</v>
+      </c>
+      <c r="E59" s="1">
+        <v>14.618</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C60" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1.088</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1.703</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1.758</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1.738</v>
+      </c>
+      <c r="E62" s="1">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0.355</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.359</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="D64" s="1">
+        <v>5.864</v>
+      </c>
+      <c r="E64" s="1">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1.886</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="D66" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="E66" s="1">
+        <v>7.467</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D67" s="1">
+        <v>13.324</v>
+      </c>
+      <c r="E67" s="1">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C68" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1.886</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2.999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1.422</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1.422</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="D70" s="1">
+        <v>3.21</v>
+      </c>
+      <c r="E70" s="1">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="D71" s="1">
+        <v>3.115</v>
+      </c>
+      <c r="E71" s="1">
+        <v>3.335</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2.163</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2.163</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="D73" s="1">
+        <v>3.062</v>
+      </c>
+      <c r="E73" s="1">
+        <v>4.024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2.635</v>
+      </c>
+      <c r="E74" s="1">
+        <v>3.388</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="D75" s="1">
+        <v>13.562</v>
+      </c>
+      <c r="E75" s="1">
+        <v>19.514</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="D77" s="1">
+        <v>2.804</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3.212</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="D78" s="1">
+        <v>4.89</v>
+      </c>
+      <c r="E78" s="1">
+        <v>6.266</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="D79" s="1">
+        <v>4.564</v>
+      </c>
+      <c r="E79" s="1">
+        <v>5.582</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D80" s="1">
+        <v>3.401</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3.401</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1.902</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2.074</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="D82" s="1">
+        <v>4.867</v>
+      </c>
+      <c r="E82" s="1">
+        <v>6.532</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1.15</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1.785</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1.987</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="C85" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="D85" s="1">
+        <v>19.926</v>
+      </c>
+      <c r="E85" s="1">
+        <v>21.456</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="D86" s="1">
+        <v>11.552</v>
+      </c>
+      <c r="E86" s="1">
+        <v>13.509</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="C87" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="D87" s="1">
+        <v>6.705</v>
+      </c>
+      <c r="E87" s="1">
+        <v>8.425</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="D88" s="1">
+        <v>25.464</v>
+      </c>
+      <c r="E88" s="1">
+        <v>34.331</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="D89" s="1">
+        <v>0.354</v>
+      </c>
+      <c r="E89" s="1">
+        <v>2.373</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="D90" s="1">
+        <v>4.021</v>
+      </c>
+      <c r="E90" s="1">
+        <v>5.096</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="D91" s="1">
+        <v>11.249</v>
+      </c>
+      <c r="E91" s="1">
+        <v>12.481</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="C92" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="D92" s="1">
+        <v>2.42</v>
+      </c>
+      <c r="E92" s="1">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="D93" s="1">
+        <v>5.427</v>
+      </c>
+      <c r="E93" s="1">
+        <v>7.272</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="D94" s="1">
+        <v>10.517</v>
+      </c>
+      <c r="E94" s="1">
+        <v>10.517</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="D95" s="1">
+        <v>3.281</v>
+      </c>
+      <c r="E95" s="1">
+        <v>4.072</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="D96" s="1">
+        <v>12.104</v>
+      </c>
+      <c r="E96" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="D97" s="1">
+        <v>4.458</v>
+      </c>
+      <c r="E97" s="1">
+        <v>6.911</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B98" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="D98" s="1">
+        <v>7.776</v>
+      </c>
+      <c r="E98" s="1">
+        <v>8.425</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B99" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="C99" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="D99" s="1">
+        <v>7.299</v>
+      </c>
+      <c r="E99" s="1">
+        <v>9.974</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="D100" s="1">
+        <v>9.62</v>
+      </c>
+      <c r="E100" s="1">
+        <v>12.93</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B101" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="D101" s="1">
+        <v>7.013</v>
+      </c>
+      <c r="E101" s="1">
+        <v>10.145</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D102" s="1">
+        <v>14.782</v>
+      </c>
+      <c r="E102" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B103" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="D103" s="1">
+        <v>42.839</v>
+      </c>
+      <c r="E103" s="1">
+        <v>65.486</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="C104" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D104" s="1">
+        <v>2.857</v>
+      </c>
+      <c r="E104" s="1">
+        <v>2.857</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B105" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="D105" s="1">
+        <v>4.088</v>
+      </c>
+      <c r="E105" s="1">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B106" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="D106" s="1">
+        <v>18.203</v>
+      </c>
+      <c r="E106" s="1">
+        <v>18.203</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B107" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="D107" s="1">
+        <v>4.445</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4.445</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="D108" s="1">
+        <v>13.202</v>
+      </c>
+      <c r="E108" s="1">
+        <v>13.202</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.58</v>
+      </c>
+      <c r="D109" s="1">
+        <v>14.903</v>
+      </c>
+      <c r="E109" s="1">
+        <v>21.683</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="D110" s="1">
+        <v>8.016</v>
+      </c>
+      <c r="E110" s="1">
+        <v>15.815</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0.58</v>
+      </c>
+      <c r="D111" s="1">
+        <v>33.229</v>
+      </c>
+      <c r="E111" s="1">
+        <v>44.183</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="D112" s="1">
+        <v>26.113</v>
+      </c>
+      <c r="E112" s="1">
+        <v>36.257</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/egg_data.xlsx
+++ b/egg_data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>精灵名称</t>
   </si>
@@ -44,337 +44,379 @@
     <t>重量最大</t>
   </si>
   <si>
+    <t>鸭吉吉</t>
+  </si>
+  <si>
+    <t>板板壳</t>
+  </si>
+  <si>
+    <t>锥尾鸟</t>
+  </si>
+  <si>
+    <t>雪绒鸟</t>
+  </si>
+  <si>
+    <t>小灵菇</t>
+  </si>
+  <si>
+    <t>石肤蜥</t>
+  </si>
+  <si>
+    <t>布是石</t>
+  </si>
+  <si>
+    <t>恶魔叮</t>
+  </si>
+  <si>
+    <t>毛毛</t>
+  </si>
+  <si>
+    <t>幽影树</t>
+  </si>
+  <si>
+    <t>小鼠獭</t>
+  </si>
+  <si>
+    <t>矿晶虫</t>
+  </si>
+  <si>
+    <t>奇丽草</t>
+  </si>
+  <si>
+    <t>丢丢</t>
+  </si>
+  <si>
+    <t>护主犬</t>
+  </si>
+  <si>
+    <t>绿耳松鼠</t>
+  </si>
+  <si>
+    <t>嘟嘟侠</t>
+  </si>
+  <si>
+    <t>小灵面</t>
+  </si>
+  <si>
+    <t>梦游</t>
+  </si>
+  <si>
+    <t>兽花蕾</t>
+  </si>
+  <si>
+    <t>伏地兽</t>
+  </si>
+  <si>
+    <t>蹦蹦种子</t>
+  </si>
+  <si>
+    <t>电咩咩</t>
+  </si>
+  <si>
+    <t>蒲公英</t>
+  </si>
+  <si>
+    <t>伊贝儿</t>
+  </si>
+  <si>
+    <t>白发懒人</t>
+  </si>
+  <si>
+    <t>海盔虫</t>
+  </si>
+  <si>
+    <t>菊花梨</t>
+  </si>
+  <si>
+    <t>小星光</t>
+  </si>
+  <si>
+    <t>一窝蜂</t>
+  </si>
+  <si>
+    <t>小夜</t>
+  </si>
+  <si>
+    <t>乖乖鸪</t>
+  </si>
+  <si>
+    <t>锤头鹳</t>
+  </si>
+  <si>
+    <t>绿草精灵</t>
+  </si>
+  <si>
+    <t>记忆石</t>
+  </si>
+  <si>
+    <t>咔咔羽毛</t>
+  </si>
+  <si>
+    <t>小草虫</t>
+  </si>
+  <si>
+    <t>绿翼鸟</t>
+  </si>
+  <si>
+    <t>阿米亚特</t>
+  </si>
+  <si>
+    <t>风铃鲨</t>
+  </si>
+  <si>
+    <t>石石</t>
+  </si>
+  <si>
+    <t>仪使者</t>
+  </si>
+  <si>
+    <t>小独角兽</t>
+  </si>
+  <si>
     <t>旋叶虫</t>
   </si>
   <si>
+    <t>小黑猫</t>
+  </si>
+  <si>
+    <t>多多</t>
+  </si>
+  <si>
+    <t>哭哭菇</t>
+  </si>
+  <si>
+    <t>恶魔狼</t>
+  </si>
+  <si>
+    <t>小电企鹅</t>
+  </si>
+  <si>
+    <t>雪豆丁</t>
+  </si>
+  <si>
+    <t>呼呼猪</t>
+  </si>
+  <si>
+    <t>雪娃娃</t>
+  </si>
+  <si>
+    <t>大耳帽兜</t>
+  </si>
+  <si>
+    <t>灵狐</t>
+  </si>
+  <si>
+    <t>公平鸽</t>
+  </si>
+  <si>
+    <t>小怂猫</t>
+  </si>
+  <si>
+    <t>小狮鹫</t>
+  </si>
+  <si>
+    <t>圆眼蜘蛛</t>
+  </si>
+  <si>
+    <t>波波螺</t>
+  </si>
+  <si>
+    <t>菇菇丁</t>
+  </si>
+  <si>
+    <t>斑斑</t>
+  </si>
+  <si>
+    <t>草头鸭</t>
+  </si>
+  <si>
+    <t>海豹战士</t>
+  </si>
+  <si>
+    <t>号儿虫</t>
+  </si>
+  <si>
+    <t>甜田螺</t>
+  </si>
+  <si>
+    <t>棋棋</t>
+  </si>
+  <si>
+    <t>奔波鼠</t>
+  </si>
+  <si>
+    <t>呆小路</t>
+  </si>
+  <si>
+    <t>逗逗</t>
+  </si>
+  <si>
+    <t>花恋蝶</t>
+  </si>
+  <si>
+    <t>伊雷龙</t>
+  </si>
+  <si>
+    <t>拉特</t>
+  </si>
+  <si>
+    <t>闪电环</t>
+  </si>
+  <si>
+    <t>小箱怪</t>
+  </si>
+  <si>
+    <t>古钟蛇</t>
+  </si>
+  <si>
+    <t>矮脚虎熊</t>
+  </si>
+  <si>
+    <t>火尾瓦特</t>
+  </si>
+  <si>
+    <t>里拉蟹</t>
+  </si>
+  <si>
+    <t>海枝枝</t>
+  </si>
+  <si>
+    <t>多西</t>
+  </si>
+  <si>
+    <t>小翼龙</t>
+  </si>
+  <si>
+    <t>电动长颈鹿</t>
+  </si>
+  <si>
+    <t>小鹏</t>
+  </si>
+  <si>
     <t>刺轮砣</t>
   </si>
   <si>
+    <t>豆丁鱼</t>
+  </si>
+  <si>
+    <t>胆小鳗鱼</t>
+  </si>
+  <si>
+    <t>翡翠水母</t>
+  </si>
+  <si>
+    <t>装洛</t>
+  </si>
+  <si>
+    <t>可爱猿</t>
+  </si>
+  <si>
+    <t>布鲁斯</t>
+  </si>
+  <si>
+    <t>治愈兔</t>
+  </si>
+  <si>
+    <t>乌达</t>
+  </si>
+  <si>
+    <t>螺旋帕帕</t>
+  </si>
+  <si>
+    <t>机械方方</t>
+  </si>
+  <si>
+    <t>可立鸡</t>
+  </si>
+  <si>
+    <t>优优</t>
+  </si>
+  <si>
+    <t>啵啵鸟</t>
+  </si>
+  <si>
+    <t>深蓝鲸</t>
+  </si>
+  <si>
+    <t>格兰种子</t>
+  </si>
+  <si>
+    <t>地鼠</t>
+  </si>
+  <si>
+    <t>黑爵士</t>
+  </si>
+  <si>
+    <t>小甲虫</t>
+  </si>
+  <si>
+    <t>圣剑侍从</t>
+  </si>
+  <si>
+    <t>吸泥鸱</t>
+  </si>
+  <si>
+    <t>大头骨龙</t>
+  </si>
+  <si>
+    <t>厉毒小萝</t>
+  </si>
+  <si>
+    <t>小帕尔</t>
+  </si>
+  <si>
+    <t>毛头小蛛</t>
+  </si>
+  <si>
     <t>画精灵</t>
   </si>
   <si>
-    <t>小鹬</t>
-  </si>
-  <si>
-    <t>菇菇丁</t>
-  </si>
-  <si>
-    <t>号儿鱼</t>
-  </si>
-  <si>
-    <t>毛毛</t>
-  </si>
-  <si>
-    <t>波波螺</t>
-  </si>
-  <si>
-    <t>逗逗</t>
-  </si>
-  <si>
     <t>书魔虫</t>
   </si>
   <si>
-    <t>矮脚爬爬</t>
-  </si>
-  <si>
-    <t>雪娃娃</t>
-  </si>
-  <si>
-    <t>棋棋</t>
-  </si>
-  <si>
-    <t>哭哭菇</t>
-  </si>
-  <si>
-    <t>螺旋帕帕</t>
-  </si>
-  <si>
-    <t>蒲公英</t>
-  </si>
-  <si>
-    <t>兽花蕾</t>
-  </si>
-  <si>
-    <t>闪电环</t>
-  </si>
-  <si>
-    <t>丢丢灵</t>
-  </si>
-  <si>
-    <t>小箱怪</t>
-  </si>
-  <si>
-    <t>小鼠獭</t>
+    <t>纸纸</t>
+  </si>
+  <si>
+    <t>扇角鸟</t>
+  </si>
+  <si>
+    <t>果冻</t>
+  </si>
+  <si>
+    <t>星尘虫</t>
+  </si>
+  <si>
+    <t>双灯鱼</t>
+  </si>
+  <si>
+    <t>月牙雪熊</t>
+  </si>
+  <si>
+    <t>曙光啵啵</t>
+  </si>
+  <si>
+    <t>柴渣虫</t>
+  </si>
+  <si>
+    <t>空空颅</t>
+  </si>
+  <si>
+    <t>粉粉星</t>
+  </si>
+  <si>
+    <t>贝瑟</t>
   </si>
   <si>
     <t>粉星仔</t>
   </si>
   <si>
-    <t>优优</t>
-  </si>
-  <si>
-    <t>石石</t>
-  </si>
-  <si>
-    <t>豆丁鱼</t>
-  </si>
-  <si>
-    <t>大耳帽兜</t>
-  </si>
-  <si>
-    <t>雪绒鸟</t>
-  </si>
-  <si>
-    <t>小灵菇</t>
-  </si>
-  <si>
-    <t>格兰种子</t>
-  </si>
-  <si>
-    <t>柴渣虫</t>
-  </si>
-  <si>
-    <t>可立鸡</t>
-  </si>
-  <si>
-    <t>甜田螺</t>
-  </si>
-  <si>
-    <t>小灵面</t>
-  </si>
-  <si>
-    <t>一窝蜂</t>
-  </si>
-  <si>
-    <t>彩蝶鲨</t>
-  </si>
-  <si>
-    <t>丢丢</t>
-  </si>
-  <si>
-    <t>奇丽草</t>
-  </si>
-  <si>
-    <t>小草虫</t>
-  </si>
-  <si>
-    <t>绿翼鸟</t>
-  </si>
-  <si>
-    <t>权杖 - 11</t>
-  </si>
-  <si>
-    <t>乌达</t>
-  </si>
-  <si>
-    <t>多多</t>
-  </si>
-  <si>
-    <t>小电企鹅</t>
-  </si>
-  <si>
-    <t>风铃鲨</t>
-  </si>
-  <si>
-    <t>布是石</t>
-  </si>
-  <si>
-    <t>公平鸽</t>
-  </si>
-  <si>
-    <t>伊贝儿</t>
-  </si>
-  <si>
-    <t>吸泥鸥</t>
-  </si>
-  <si>
-    <t>奔波鼠</t>
-  </si>
-  <si>
-    <t>仪使者</t>
-  </si>
-  <si>
-    <t>拉特</t>
-  </si>
-  <si>
-    <t>矿晶虫</t>
-  </si>
-  <si>
-    <t>地鼠</t>
-  </si>
-  <si>
-    <t>石肤蜥</t>
-  </si>
-  <si>
-    <t>草头鸭</t>
-  </si>
-  <si>
-    <t>厉毒小萝</t>
-  </si>
-  <si>
-    <t>呼呼</t>
-  </si>
-  <si>
-    <t>阿米樱</t>
-  </si>
-  <si>
-    <t>小黑猫</t>
-  </si>
-  <si>
-    <t>圆眼蜘蛛</t>
-  </si>
-  <si>
-    <t>乖乖鸫</t>
-  </si>
-  <si>
-    <t>梦游</t>
-  </si>
-  <si>
-    <t>双灯鱼</t>
-  </si>
-  <si>
-    <t>绿耳松鼠</t>
-  </si>
-  <si>
-    <t>小怂猫</t>
-  </si>
-  <si>
-    <t>翡翠水母</t>
-  </si>
-  <si>
-    <t>小夜</t>
-  </si>
-  <si>
-    <t>花怨鳗</t>
-  </si>
-  <si>
-    <t>小甲虫</t>
-  </si>
-  <si>
-    <t>海盗虫</t>
-  </si>
-  <si>
-    <t>蹦蹦种子</t>
-  </si>
-  <si>
-    <t>板板壳</t>
-  </si>
-  <si>
-    <t>灵狐</t>
-  </si>
-  <si>
-    <t>阿米亚特</t>
-  </si>
-  <si>
-    <t>喵喵</t>
-  </si>
-  <si>
-    <t>电咩咩</t>
-  </si>
-  <si>
-    <t>锥尾羊</t>
-  </si>
-  <si>
-    <t>治愈兔</t>
-  </si>
-  <si>
-    <t>呼呼猪</t>
-  </si>
-  <si>
-    <t>呆小路</t>
-  </si>
-  <si>
-    <t>护主犬</t>
-  </si>
-  <si>
-    <t>粉粉星</t>
-  </si>
-  <si>
-    <t>菊花梨</t>
-  </si>
-  <si>
-    <t>嘟嘟煲</t>
-  </si>
-  <si>
-    <t>幽影树</t>
-  </si>
-  <si>
-    <t>火尾瓦特</t>
-  </si>
-  <si>
-    <t>海豹战士</t>
-  </si>
-  <si>
-    <t>海枝枝</t>
-  </si>
-  <si>
-    <t>小帕尔</t>
-  </si>
-  <si>
-    <t>电动长颈鹿</t>
-  </si>
-  <si>
-    <t>多西</t>
-  </si>
-  <si>
-    <t>鸭吉吉</t>
-  </si>
-  <si>
-    <t>可爱猿</t>
-  </si>
-  <si>
-    <t>绿草精灵</t>
-  </si>
-  <si>
-    <t>伊雷龙</t>
-  </si>
-  <si>
-    <t>小狮鹫</t>
-  </si>
-  <si>
-    <t>白发懒人</t>
-  </si>
-  <si>
-    <t>大头骨龙</t>
-  </si>
-  <si>
-    <t>小星光</t>
-  </si>
-  <si>
-    <t>胆小鳗鱼</t>
-  </si>
-  <si>
-    <t>里拉鳐</t>
-  </si>
-  <si>
-    <t>圣剑侍从</t>
-  </si>
-  <si>
-    <t>古钟蛇</t>
-  </si>
-  <si>
-    <t>雪豆丁</t>
-  </si>
-  <si>
-    <t>锤头鹳</t>
-  </si>
-  <si>
-    <t>雪蛮人</t>
-  </si>
-  <si>
-    <t>小翼龙</t>
-  </si>
-  <si>
-    <t>小独角兽</t>
+    <t>布瓜蜗</t>
   </si>
   <si>
     <t>火红尾</t>
   </si>
   <si>
-    <t>记忆石</t>
-  </si>
-  <si>
-    <t>恶魔狼</t>
+    <t>春团</t>
   </si>
 </sst>
 </file>
@@ -850,19 +892,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -871,7 +913,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -997,7 +1039,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1344,7 +1386,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1369,16 +1411,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>0.04</v>
+        <v>0.36</v>
       </c>
       <c r="C2" s="1">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="D2" s="1">
-        <v>0.057</v>
+        <v>6.42</v>
       </c>
       <c r="E2" s="1">
-        <v>0.07</v>
+        <v>6.727</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1386,16 +1428,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="C3" s="1">
-        <v>0.13</v>
+        <v>0.304</v>
       </c>
       <c r="D3" s="1">
-        <v>1.452</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1">
-        <v>1.554</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1403,16 +1445,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="1">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="C4" s="1">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="D4" s="1">
-        <v>0.353</v>
+        <v>6.238</v>
       </c>
       <c r="E4" s="1">
-        <v>0.415</v>
+        <v>6.345</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1420,16 +1462,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="1">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="D5" s="1">
-        <v>0.53</v>
+        <v>1.364</v>
       </c>
       <c r="E5" s="1">
-        <v>0.7</v>
+        <v>1.789</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1437,16 +1479,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="1">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="1">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="D6" s="1">
-        <v>0.447</v>
+        <v>2.827</v>
       </c>
       <c r="E6" s="1">
-        <v>0.447</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1454,16 +1496,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="1">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="C7" s="1">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="D7" s="1">
-        <v>1.426</v>
+        <v>12.252</v>
       </c>
       <c r="E7" s="1">
-        <v>1.426</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1471,16 +1513,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="1">
-        <v>0.14</v>
+        <v>0.168</v>
       </c>
       <c r="C8" s="1">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="D8" s="1">
-        <v>1.17</v>
+        <v>7.4</v>
       </c>
       <c r="E8" s="1">
-        <v>1.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1488,16 +1530,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="1">
-        <v>0.14</v>
+        <v>0.156</v>
       </c>
       <c r="C9" s="1">
-        <v>0.14</v>
+        <v>0.224</v>
       </c>
       <c r="D9" s="1">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="E9" s="1">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1505,16 +1547,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="1">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="C10" s="1">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="D10" s="1">
-        <v>0.23</v>
+        <v>1.2</v>
       </c>
       <c r="E10" s="1">
-        <v>0.287</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1522,16 +1564,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="1">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="C11" s="1">
-        <v>0.15</v>
+        <v>0.368</v>
       </c>
       <c r="D11" s="1">
-        <v>1.153</v>
+        <v>12.01</v>
       </c>
       <c r="E11" s="1">
-        <v>1.153</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1539,16 +1581,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="1">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="C12" s="1">
-        <v>0.18</v>
+        <v>0.212</v>
       </c>
       <c r="D12" s="1">
-        <v>1.184</v>
+        <v>2.506</v>
       </c>
       <c r="E12" s="1">
-        <v>1.646</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1556,16 +1598,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="1">
-        <v>0.13</v>
+        <v>0.216</v>
       </c>
       <c r="C13" s="1">
-        <v>0.17</v>
+        <v>0.308</v>
       </c>
       <c r="D13" s="1">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="E13" s="1">
-        <v>3.223</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1573,16 +1615,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="1">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="C14" s="1">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="D14" s="1">
-        <v>4.053</v>
+        <v>1.706</v>
       </c>
       <c r="E14" s="1">
-        <v>4.651</v>
+        <v>2.204</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1593,13 +1635,13 @@
         <v>0.15</v>
       </c>
       <c r="C15" s="1">
-        <v>0.18</v>
+        <v>0.204</v>
       </c>
       <c r="D15" s="1">
-        <v>0.749</v>
+        <v>1.519</v>
       </c>
       <c r="E15" s="1">
-        <v>1.064</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1607,16 +1649,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="1">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="C16" s="1">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="D16" s="1">
-        <v>0.812</v>
+        <v>5.078</v>
       </c>
       <c r="E16" s="1">
-        <v>1.571</v>
+        <v>6.038</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1624,16 +1666,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="1">
-        <v>0.13</v>
+        <v>0.188</v>
       </c>
       <c r="C17" s="1">
-        <v>0.21</v>
+        <v>0.272</v>
       </c>
       <c r="D17" s="1">
-        <v>0.037</v>
+        <v>1.4</v>
       </c>
       <c r="E17" s="1">
-        <v>0.117</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1641,16 +1683,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="1">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="C18" s="1">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="D18" s="1">
-        <v>1.559</v>
+        <v>19.926</v>
       </c>
       <c r="E18" s="1">
-        <v>2.171</v>
+        <v>21.456</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1661,13 +1703,13 @@
         <v>0.16</v>
       </c>
       <c r="C19" s="1">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="D19" s="1">
-        <v>0.847</v>
+        <v>0.036</v>
       </c>
       <c r="E19" s="1">
-        <v>1.187</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1675,16 +1717,16 @@
         <v>23</v>
       </c>
       <c r="B20" s="1">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D20" s="1">
-        <v>1.299</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="1">
-        <v>2.196</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1692,16 +1734,16 @@
         <v>24</v>
       </c>
       <c r="B21" s="1">
-        <v>0.18</v>
+        <v>0.152</v>
       </c>
       <c r="C21" s="1">
         <v>0.18</v>
       </c>
       <c r="D21" s="1">
-        <v>2.479</v>
+        <v>1.7</v>
       </c>
       <c r="E21" s="1">
-        <v>2.479</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1709,16 +1751,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="1">
-        <v>0.17</v>
+        <v>0.208</v>
       </c>
       <c r="C22" s="1">
-        <v>0.19</v>
+        <v>0.296</v>
       </c>
       <c r="D22" s="1">
-        <v>2.492</v>
+        <v>4.96</v>
       </c>
       <c r="E22" s="1">
-        <v>2.727</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1726,16 +1768,16 @@
         <v>26</v>
       </c>
       <c r="B23" s="1">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="C23" s="1">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="D23" s="1">
-        <v>3.714</v>
+        <v>1.636</v>
       </c>
       <c r="E23" s="1">
-        <v>4.398</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1743,16 +1785,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="1">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="C24" s="1">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="D24" s="1">
-        <v>1.171</v>
+        <v>2.578</v>
       </c>
       <c r="E24" s="1">
-        <v>1.315</v>
+        <v>3.604</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1760,16 +1802,16 @@
         <v>28</v>
       </c>
       <c r="B25" s="1">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="C25" s="1">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="D25" s="1">
-        <v>21.471</v>
+        <v>0.038</v>
       </c>
       <c r="E25" s="1">
-        <v>29.809</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1777,16 +1819,16 @@
         <v>29</v>
       </c>
       <c r="B26" s="1">
-        <v>0.13</v>
+        <v>0.176</v>
       </c>
       <c r="C26" s="1">
-        <v>0.23</v>
+        <v>0.248</v>
       </c>
       <c r="D26" s="1">
-        <v>0.434</v>
+        <v>1.32</v>
       </c>
       <c r="E26" s="1">
-        <v>1.203</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1794,16 +1836,16 @@
         <v>30</v>
       </c>
       <c r="B27" s="1">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="C27" s="1">
-        <v>0.2</v>
+        <v>0.412</v>
       </c>
       <c r="D27" s="1">
-        <v>2.937</v>
+        <v>7.957</v>
       </c>
       <c r="E27" s="1">
-        <v>4.029</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1811,16 +1853,16 @@
         <v>31</v>
       </c>
       <c r="B28" s="1">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="C28" s="1">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="D28" s="1">
-        <v>1.166</v>
+        <v>3.077</v>
       </c>
       <c r="E28" s="1">
-        <v>1.793</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1828,16 +1870,16 @@
         <v>32</v>
       </c>
       <c r="B29" s="1">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="C29" s="1">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="D29" s="1">
-        <v>2.078</v>
+        <v>1.987</v>
       </c>
       <c r="E29" s="1">
-        <v>2.078</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1845,16 +1887,16 @@
         <v>33</v>
       </c>
       <c r="B30" s="1">
-        <v>0.18</v>
+        <v>0.312</v>
       </c>
       <c r="C30" s="1">
-        <v>0.2</v>
+        <v>0.448</v>
       </c>
       <c r="D30" s="1">
-        <v>1.408</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1">
-        <v>1.678</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1865,13 +1907,13 @@
         <v>0.19</v>
       </c>
       <c r="C31" s="1">
-        <v>0.2</v>
+        <v>0.208</v>
       </c>
       <c r="D31" s="1">
-        <v>5.247</v>
+        <v>1.851</v>
       </c>
       <c r="E31" s="1">
-        <v>5.976</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1879,16 +1921,16 @@
         <v>35</v>
       </c>
       <c r="B32" s="1">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="C32" s="1">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="D32" s="1">
-        <v>2.022</v>
+        <v>1.886</v>
       </c>
       <c r="E32" s="1">
-        <v>2.27</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1896,16 +1938,16 @@
         <v>36</v>
       </c>
       <c r="B33" s="1">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="C33" s="1">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="D33" s="1">
-        <v>2.627</v>
+        <v>1.738</v>
       </c>
       <c r="E33" s="1">
-        <v>3.457</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1913,16 +1955,16 @@
         <v>37</v>
       </c>
       <c r="B34" s="1">
-        <v>0.16</v>
+        <v>0.63</v>
       </c>
       <c r="C34" s="1">
-        <v>0.23</v>
+        <v>0.63</v>
       </c>
       <c r="D34" s="1">
-        <v>0.036</v>
+        <v>25.539</v>
       </c>
       <c r="E34" s="1">
-        <v>0.058</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1930,16 +1972,16 @@
         <v>38</v>
       </c>
       <c r="B35" s="1">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="C35" s="1">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="D35" s="1">
-        <v>1.666</v>
+        <v>3.415</v>
       </c>
       <c r="E35" s="1">
-        <v>2.15</v>
+        <v>4.029</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1947,16 +1989,16 @@
         <v>39</v>
       </c>
       <c r="B36" s="1">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="C36" s="1">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="D36" s="1">
-        <v>5.585</v>
+        <v>33.61</v>
       </c>
       <c r="E36" s="1">
-        <v>5.85</v>
+        <v>43.575</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1964,16 +2006,16 @@
         <v>40</v>
       </c>
       <c r="B37" s="1">
-        <v>0.21</v>
+        <v>0.248</v>
       </c>
       <c r="C37" s="1">
-        <v>0.21</v>
+        <v>0.356</v>
       </c>
       <c r="D37" s="1">
-        <v>2.355</v>
+        <v>1.048</v>
       </c>
       <c r="E37" s="1">
-        <v>2.355</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1981,16 +2023,16 @@
         <v>41</v>
       </c>
       <c r="B38" s="1">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="C38" s="1">
-        <v>0.22</v>
+        <v>0.268</v>
       </c>
       <c r="D38" s="1">
-        <v>1.842</v>
+        <v>0.84</v>
       </c>
       <c r="E38" s="1">
-        <v>2.145</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1998,16 +2040,16 @@
         <v>42</v>
       </c>
       <c r="B39" s="1">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="C39" s="1">
-        <v>0.22</v>
+        <v>0.244</v>
       </c>
       <c r="D39" s="1">
-        <v>0.777</v>
+        <v>1.35</v>
       </c>
       <c r="E39" s="1">
-        <v>0.934</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2015,16 +2057,16 @@
         <v>43</v>
       </c>
       <c r="B40" s="1">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="C40" s="1">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="D40" s="1">
-        <v>1.304</v>
+        <v>14.618</v>
       </c>
       <c r="E40" s="1">
-        <v>1.471</v>
+        <v>18.153</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2032,16 +2074,16 @@
         <v>44</v>
       </c>
       <c r="B41" s="1">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="C41" s="1">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="D41" s="1">
-        <v>12.073</v>
+        <v>4.697</v>
       </c>
       <c r="E41" s="1">
-        <v>12.904</v>
+        <v>5.134</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2049,16 +2091,16 @@
         <v>45</v>
       </c>
       <c r="B42" s="1">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="C42" s="1">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="D42" s="1">
-        <v>1.65</v>
+        <v>21.405</v>
       </c>
       <c r="E42" s="1">
-        <v>2.361</v>
+        <v>29.626</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2066,16 +2108,16 @@
         <v>46</v>
       </c>
       <c r="B43" s="1">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="C43" s="1">
-        <v>0.25</v>
+        <v>0.232</v>
       </c>
       <c r="D43" s="1">
-        <v>5.21</v>
+        <v>7.62</v>
       </c>
       <c r="E43" s="1">
-        <v>6.85</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2083,16 +2125,16 @@
         <v>47</v>
       </c>
       <c r="B44" s="1">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="C44" s="1">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="D44" s="1">
-        <v>1.835</v>
+        <v>15.95</v>
       </c>
       <c r="E44" s="1">
-        <v>2.017</v>
+        <v>22.234</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2100,16 +2142,16 @@
         <v>48</v>
       </c>
       <c r="B45" s="1">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="C45" s="1">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="D45" s="1">
-        <v>6.01</v>
+        <v>0.072</v>
       </c>
       <c r="E45" s="1">
-        <v>6.204</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2117,16 +2159,16 @@
         <v>49</v>
       </c>
       <c r="B46" s="1">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="C46" s="1">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="D46" s="1">
-        <v>9.627</v>
+        <v>1.24</v>
       </c>
       <c r="E46" s="1">
-        <v>12.703</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2134,16 +2176,16 @@
         <v>50</v>
       </c>
       <c r="B47" s="1">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="C47" s="1">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D47" s="1">
-        <v>1.213</v>
+        <v>5.21</v>
       </c>
       <c r="E47" s="1">
-        <v>1.452</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2151,16 +2193,16 @@
         <v>51</v>
       </c>
       <c r="B48" s="1">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="C48" s="1">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="D48" s="1">
-        <v>1.603</v>
+        <v>0.802</v>
       </c>
       <c r="E48" s="1">
-        <v>1.603</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2168,16 +2210,16 @@
         <v>52</v>
       </c>
       <c r="B49" s="1">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="C49" s="1">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="D49" s="1">
-        <v>3.365</v>
+        <v>29.725</v>
       </c>
       <c r="E49" s="1">
-        <v>3.528</v>
+        <v>36.615</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2191,10 +2233,10 @@
         <v>0.23</v>
       </c>
       <c r="D50" s="1">
-        <v>2.126</v>
+        <v>2.078</v>
       </c>
       <c r="E50" s="1">
-        <v>2.126</v>
+        <v>2.156</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2202,16 +2244,16 @@
         <v>54</v>
       </c>
       <c r="B51" s="1">
-        <v>0.23</v>
+        <v>0.344</v>
       </c>
       <c r="C51" s="1">
-        <v>0.23</v>
+        <v>0.492</v>
       </c>
       <c r="D51" s="1">
-        <v>12.203</v>
+        <v>3.8</v>
       </c>
       <c r="E51" s="1">
-        <v>12.203</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2219,16 +2261,16 @@
         <v>55</v>
       </c>
       <c r="B52" s="1">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="C52" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D52" s="1">
-        <v>3.107</v>
+        <v>3.401</v>
       </c>
       <c r="E52" s="1">
-        <v>3.434</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2236,16 +2278,16 @@
         <v>56</v>
       </c>
       <c r="B53" s="1">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="C53" s="1">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="D53" s="1">
-        <v>2.101</v>
+        <v>2.589</v>
       </c>
       <c r="E53" s="1">
-        <v>2.156</v>
+        <v>3.223</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2253,16 +2295,16 @@
         <v>57</v>
       </c>
       <c r="B54" s="1">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="C54" s="1">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="D54" s="1">
-        <v>0.75</v>
+        <v>3.216</v>
       </c>
       <c r="E54" s="1">
-        <v>0.933</v>
+        <v>4.144</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2270,16 +2312,16 @@
         <v>58</v>
       </c>
       <c r="B55" s="1">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="C55" s="1">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="D55" s="1">
-        <v>8.091</v>
+        <v>3.123</v>
       </c>
       <c r="E55" s="1">
-        <v>11.642</v>
+        <v>3.179</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2287,16 +2329,16 @@
         <v>59</v>
       </c>
       <c r="B56" s="1">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="C56" s="1">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="D56" s="1">
-        <v>1.902</v>
+        <v>1</v>
       </c>
       <c r="E56" s="1">
-        <v>2.336</v>
+        <v>1.576</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2304,16 +2346,16 @@
         <v>60</v>
       </c>
       <c r="B57" s="1">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="C57" s="1">
-        <v>0.27</v>
+        <v>0.336</v>
       </c>
       <c r="D57" s="1">
-        <v>3.374</v>
+        <v>8.146</v>
       </c>
       <c r="E57" s="1">
-        <v>5.927</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2321,16 +2363,16 @@
         <v>61</v>
       </c>
       <c r="B58" s="1">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="C58" s="1">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="D58" s="1">
-        <v>2.417</v>
+        <v>4.309</v>
       </c>
       <c r="E58" s="1">
-        <v>3.133</v>
+        <v>6.526</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2338,16 +2380,16 @@
         <v>62</v>
       </c>
       <c r="B59" s="1">
-        <v>0.25</v>
+        <v>0.192</v>
       </c>
       <c r="C59" s="1">
-        <v>0.25</v>
+        <v>0.272</v>
       </c>
       <c r="D59" s="1">
-        <v>14.618</v>
+        <v>1.4</v>
       </c>
       <c r="E59" s="1">
-        <v>14.618</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2355,16 +2397,16 @@
         <v>63</v>
       </c>
       <c r="B60" s="1">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="C60" s="1">
-        <v>0.27</v>
+        <v>0.168</v>
       </c>
       <c r="D60" s="1">
-        <v>1.088</v>
+        <v>1.895</v>
       </c>
       <c r="E60" s="1">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2372,16 +2414,16 @@
         <v>64</v>
       </c>
       <c r="B61" s="1">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="C61" s="1">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="D61" s="1">
-        <v>1.703</v>
+        <v>0.477</v>
       </c>
       <c r="E61" s="1">
-        <v>1.758</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2389,16 +2431,16 @@
         <v>65</v>
       </c>
       <c r="B62" s="1">
-        <v>0.23</v>
+        <v>0.188</v>
       </c>
       <c r="C62" s="1">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="D62" s="1">
-        <v>1.738</v>
+        <v>1.916</v>
       </c>
       <c r="E62" s="1">
-        <v>2.05</v>
+        <v>2.468</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2406,16 +2448,16 @@
         <v>66</v>
       </c>
       <c r="B63" s="1">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="C63" s="1">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="D63" s="1">
-        <v>0.355</v>
+        <v>1.999</v>
       </c>
       <c r="E63" s="1">
-        <v>0.359</v>
+        <v>2.357</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2423,16 +2465,16 @@
         <v>67</v>
       </c>
       <c r="B64" s="1">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="C64" s="1">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="D64" s="1">
-        <v>5.864</v>
+        <v>26</v>
       </c>
       <c r="E64" s="1">
-        <v>6.58</v>
+        <v>31.078</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2440,16 +2482,16 @@
         <v>68</v>
       </c>
       <c r="B65" s="1">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="C65" s="1">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="D65" s="1">
-        <v>1.886</v>
+        <v>1.419</v>
       </c>
       <c r="E65" s="1">
-        <v>2.19</v>
+        <v>1.688</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2457,16 +2499,16 @@
         <v>69</v>
       </c>
       <c r="B66" s="1">
-        <v>0.25</v>
+        <v>0.164</v>
       </c>
       <c r="C66" s="1">
-        <v>0.28</v>
+        <v>0.232</v>
       </c>
       <c r="D66" s="1">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="E66" s="1">
-        <v>7.467</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2474,16 +2516,16 @@
         <v>70</v>
       </c>
       <c r="B67" s="1">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="C67" s="1">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="D67" s="1">
-        <v>13.324</v>
+        <v>5.306</v>
       </c>
       <c r="E67" s="1">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2494,13 +2536,13 @@
         <v>0.23</v>
       </c>
       <c r="C68" s="1">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="D68" s="1">
-        <v>1.886</v>
+        <v>2.126</v>
       </c>
       <c r="E68" s="1">
-        <v>2.999</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2508,16 +2550,16 @@
         <v>72</v>
       </c>
       <c r="B69" s="1">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="C69" s="1">
         <v>0.27</v>
       </c>
       <c r="D69" s="1">
-        <v>1.422</v>
+        <v>1.624</v>
       </c>
       <c r="E69" s="1">
-        <v>1.422</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2525,16 +2567,16 @@
         <v>73</v>
       </c>
       <c r="B70" s="1">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="C70" s="1">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="D70" s="1">
-        <v>3.21</v>
+        <v>0.216</v>
       </c>
       <c r="E70" s="1">
-        <v>3.21</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2542,16 +2584,16 @@
         <v>74</v>
       </c>
       <c r="B71" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C71" s="1">
         <v>0.27</v>
       </c>
-      <c r="C71" s="1">
-        <v>0.29</v>
-      </c>
       <c r="D71" s="1">
-        <v>3.115</v>
+        <v>1.019</v>
       </c>
       <c r="E71" s="1">
-        <v>3.335</v>
+        <v>1.319</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2559,16 +2601,16 @@
         <v>75</v>
       </c>
       <c r="B72" s="1">
-        <v>0.28</v>
+        <v>0.288</v>
       </c>
       <c r="C72" s="1">
-        <v>0.28</v>
+        <v>0.376</v>
       </c>
       <c r="D72" s="1">
-        <v>2.163</v>
+        <v>10.88</v>
       </c>
       <c r="E72" s="1">
-        <v>2.163</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2576,16 +2618,16 @@
         <v>76</v>
       </c>
       <c r="B73" s="1">
-        <v>0.25</v>
+        <v>0.196</v>
       </c>
       <c r="C73" s="1">
-        <v>0.31</v>
+        <v>0.244</v>
       </c>
       <c r="D73" s="1">
-        <v>3.062</v>
+        <v>3.08</v>
       </c>
       <c r="E73" s="1">
-        <v>4.024</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2593,16 +2635,16 @@
         <v>77</v>
       </c>
       <c r="B74" s="1">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="C74" s="1">
-        <v>0.32</v>
+        <v>0.184</v>
       </c>
       <c r="D74" s="1">
-        <v>2.635</v>
+        <v>0.847</v>
       </c>
       <c r="E74" s="1">
-        <v>3.388</v>
+        <v>1.313</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2610,16 +2652,16 @@
         <v>78</v>
       </c>
       <c r="B75" s="1">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="C75" s="1">
-        <v>0.33</v>
+        <v>0.184</v>
       </c>
       <c r="D75" s="1">
-        <v>13.562</v>
+        <v>2.479</v>
       </c>
       <c r="E75" s="1">
-        <v>19.514</v>
+        <v>2.724</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2627,16 +2669,16 @@
         <v>79</v>
       </c>
       <c r="B76" s="1">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="C76" s="1">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="D76" s="1">
-        <v>1.7</v>
+        <v>2.857</v>
       </c>
       <c r="E76" s="1">
-        <v>1.7</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2644,16 +2686,16 @@
         <v>80</v>
       </c>
       <c r="B77" s="1">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="C77" s="1">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="D77" s="1">
-        <v>2.804</v>
+        <v>1.327</v>
       </c>
       <c r="E77" s="1">
-        <v>3.212</v>
+        <v>1.654</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2661,16 +2703,16 @@
         <v>81</v>
       </c>
       <c r="B78" s="1">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="C78" s="1">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="D78" s="1">
-        <v>4.89</v>
+        <v>6.612</v>
       </c>
       <c r="E78" s="1">
-        <v>6.266</v>
+        <v>8.425</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2678,16 +2720,16 @@
         <v>82</v>
       </c>
       <c r="B79" s="1">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="C79" s="1">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="D79" s="1">
-        <v>4.564</v>
+        <v>18</v>
       </c>
       <c r="E79" s="1">
-        <v>5.582</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2695,16 +2737,16 @@
         <v>83</v>
       </c>
       <c r="B80" s="1">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="C80" s="1">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="D80" s="1">
-        <v>3.401</v>
+        <v>1.881</v>
       </c>
       <c r="E80" s="1">
-        <v>3.401</v>
+        <v>2.373</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2712,16 +2754,16 @@
         <v>84</v>
       </c>
       <c r="B81" s="1">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="C81" s="1">
-        <v>0.31</v>
+        <v>0.376</v>
       </c>
       <c r="D81" s="1">
-        <v>1.902</v>
+        <v>2.28</v>
       </c>
       <c r="E81" s="1">
-        <v>2.074</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2729,16 +2771,16 @@
         <v>85</v>
       </c>
       <c r="B82" s="1">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="C82" s="1">
-        <v>0.36</v>
+        <v>0.348</v>
       </c>
       <c r="D82" s="1">
-        <v>4.867</v>
+        <v>12.146</v>
       </c>
       <c r="E82" s="1">
-        <v>6.532</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2749,13 +2791,13 @@
         <v>0.32</v>
       </c>
       <c r="C83" s="1">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="D83" s="1">
-        <v>1.15</v>
+        <v>11.249</v>
       </c>
       <c r="E83" s="1">
-        <v>1.15</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2763,16 +2805,16 @@
         <v>87</v>
       </c>
       <c r="B84" s="1">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="C84" s="1">
-        <v>0.33</v>
+        <v>0.144</v>
       </c>
       <c r="D84" s="1">
-        <v>1.785</v>
+        <v>0.56</v>
       </c>
       <c r="E84" s="1">
-        <v>1.987</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2780,16 +2822,16 @@
         <v>88</v>
       </c>
       <c r="B85" s="1">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="C85" s="1">
-        <v>0.33</v>
+        <v>0.124</v>
       </c>
       <c r="D85" s="1">
-        <v>19.926</v>
+        <v>1.207</v>
       </c>
       <c r="E85" s="1">
-        <v>21.456</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2797,16 +2839,16 @@
         <v>89</v>
       </c>
       <c r="B86" s="1">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="C86" s="1">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
       <c r="D86" s="1">
-        <v>11.552</v>
+        <v>0.437</v>
       </c>
       <c r="E86" s="1">
-        <v>13.509</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2814,16 +2856,16 @@
         <v>90</v>
       </c>
       <c r="B87" s="1">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="C87" s="1">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="D87" s="1">
-        <v>6.705</v>
+        <v>10.145</v>
       </c>
       <c r="E87" s="1">
-        <v>8.425</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2831,16 +2873,16 @@
         <v>91</v>
       </c>
       <c r="B88" s="1">
+        <v>0.196</v>
+      </c>
+      <c r="C88" s="1">
         <v>0.28</v>
       </c>
-      <c r="C88" s="1">
-        <v>0.38</v>
-      </c>
       <c r="D88" s="1">
-        <v>25.464</v>
+        <v>12.6</v>
       </c>
       <c r="E88" s="1">
-        <v>34.331</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2848,16 +2890,16 @@
         <v>92</v>
       </c>
       <c r="B89" s="1">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="C89" s="1">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="D89" s="1">
-        <v>0.354</v>
+        <v>3</v>
       </c>
       <c r="E89" s="1">
-        <v>2.373</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2865,16 +2907,16 @@
         <v>93</v>
       </c>
       <c r="B90" s="1">
-        <v>0.31</v>
+        <v>0.276</v>
       </c>
       <c r="C90" s="1">
-        <v>0.37</v>
+        <v>0.392</v>
       </c>
       <c r="D90" s="1">
-        <v>4.021</v>
+        <v>8.4</v>
       </c>
       <c r="E90" s="1">
-        <v>5.096</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2882,16 +2924,16 @@
         <v>94</v>
       </c>
       <c r="B91" s="1">
-        <v>0.32</v>
+        <v>0.212</v>
       </c>
       <c r="C91" s="1">
-        <v>0.36</v>
+        <v>0.304</v>
       </c>
       <c r="D91" s="1">
-        <v>11.249</v>
+        <v>0.96</v>
       </c>
       <c r="E91" s="1">
-        <v>12.481</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2899,16 +2941,16 @@
         <v>95</v>
       </c>
       <c r="B92" s="1">
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
       <c r="C92" s="1">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="D92" s="1">
-        <v>2.42</v>
+        <v>4.221</v>
       </c>
       <c r="E92" s="1">
-        <v>2.42</v>
+        <v>4.713</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2916,16 +2958,16 @@
         <v>96</v>
       </c>
       <c r="B93" s="1">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="C93" s="1">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="D93" s="1">
-        <v>5.427</v>
+        <v>1.756</v>
       </c>
       <c r="E93" s="1">
-        <v>7.272</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2933,16 +2975,16 @@
         <v>97</v>
       </c>
       <c r="B94" s="1">
-        <v>0.36</v>
+        <v>0.15</v>
       </c>
       <c r="C94" s="1">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="D94" s="1">
-        <v>10.517</v>
+        <v>0.812</v>
       </c>
       <c r="E94" s="1">
-        <v>10.517</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2950,16 +2992,16 @@
         <v>98</v>
       </c>
       <c r="B95" s="1">
-        <v>0.3</v>
+        <v>0.168</v>
       </c>
       <c r="C95" s="1">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
       <c r="D95" s="1">
-        <v>3.281</v>
+        <v>3.2</v>
       </c>
       <c r="E95" s="1">
-        <v>4.072</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2967,16 +3009,16 @@
         <v>99</v>
       </c>
       <c r="B96" s="1">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="C96" s="1">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="D96" s="1">
-        <v>12.104</v>
+        <v>1.665</v>
       </c>
       <c r="E96" s="1">
-        <v>12.4</v>
+        <v>2.435</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2984,16 +3026,16 @@
         <v>100</v>
       </c>
       <c r="B97" s="1">
-        <v>0.31</v>
+        <v>0.152</v>
       </c>
       <c r="C97" s="1">
-        <v>0.42</v>
+        <v>0.224</v>
       </c>
       <c r="D97" s="1">
-        <v>4.458</v>
+        <v>1.212</v>
       </c>
       <c r="E97" s="1">
-        <v>6.911</v>
+        <v>1.636</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3001,16 +3043,16 @@
         <v>101</v>
       </c>
       <c r="B98" s="1">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="C98" s="1">
-        <v>0.39</v>
+        <v>0.86</v>
       </c>
       <c r="D98" s="1">
-        <v>7.776</v>
+        <v>35.8</v>
       </c>
       <c r="E98" s="1">
-        <v>8.425</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3018,16 +3060,16 @@
         <v>102</v>
       </c>
       <c r="B99" s="1">
-        <v>0.36</v>
+        <v>0.8</v>
       </c>
       <c r="C99" s="1">
-        <v>0.39</v>
+        <v>1.06</v>
       </c>
       <c r="D99" s="1">
-        <v>7.299</v>
+        <v>258</v>
       </c>
       <c r="E99" s="1">
-        <v>9.974</v>
+        <v>280</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3035,16 +3077,16 @@
         <v>103</v>
       </c>
       <c r="B100" s="1">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="C100" s="1">
-        <v>0.42</v>
+        <v>0.228</v>
       </c>
       <c r="D100" s="1">
-        <v>9.62</v>
+        <v>1.4</v>
       </c>
       <c r="E100" s="1">
-        <v>12.93</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3052,16 +3094,16 @@
         <v>104</v>
       </c>
       <c r="B101" s="1">
-        <v>0.33</v>
+        <v>0.184</v>
       </c>
       <c r="C101" s="1">
-        <v>0.43</v>
+        <v>0.264</v>
       </c>
       <c r="D101" s="1">
-        <v>7.013</v>
+        <v>0.72</v>
       </c>
       <c r="E101" s="1">
-        <v>10.145</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3069,16 +3111,16 @@
         <v>105</v>
       </c>
       <c r="B102" s="1">
-        <v>0.41</v>
+        <v>0.14</v>
       </c>
       <c r="C102" s="1">
-        <v>0.44</v>
+        <v>0.184</v>
       </c>
       <c r="D102" s="1">
-        <v>14.782</v>
+        <v>1.3</v>
       </c>
       <c r="E102" s="1">
-        <v>18</v>
+        <v>2.008</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3086,16 +3128,16 @@
         <v>106</v>
       </c>
       <c r="B103" s="1">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="C103" s="1">
-        <v>0.48</v>
+        <v>0.27</v>
       </c>
       <c r="D103" s="1">
-        <v>42.839</v>
+        <v>3.147</v>
       </c>
       <c r="E103" s="1">
-        <v>65.486</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3103,16 +3145,16 @@
         <v>107</v>
       </c>
       <c r="B104" s="1">
-        <v>0.44</v>
+        <v>0.376</v>
       </c>
       <c r="C104" s="1">
-        <v>0.44</v>
+        <v>0.472</v>
       </c>
       <c r="D104" s="1">
-        <v>2.857</v>
+        <v>46.28</v>
       </c>
       <c r="E104" s="1">
-        <v>2.857</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3120,16 +3162,16 @@
         <v>108</v>
       </c>
       <c r="B105" s="1">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="C105" s="1">
-        <v>0.47</v>
+        <v>0.284</v>
       </c>
       <c r="D105" s="1">
-        <v>4.088</v>
+        <v>3.8</v>
       </c>
       <c r="E105" s="1">
-        <v>4.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3137,16 +3179,16 @@
         <v>109</v>
       </c>
       <c r="B106" s="1">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C106" s="1">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="D106" s="1">
-        <v>18.203</v>
+        <v>9.636</v>
       </c>
       <c r="E106" s="1">
-        <v>18.203</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3154,16 +3196,16 @@
         <v>110</v>
       </c>
       <c r="B107" s="1">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="C107" s="1">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="D107" s="1">
-        <v>4.445</v>
+        <v>3.492</v>
       </c>
       <c r="E107" s="1">
-        <v>4.445</v>
+        <v>5.968</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3171,16 +3213,16 @@
         <v>111</v>
       </c>
       <c r="B108" s="1">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="C108" s="1">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="D108" s="1">
-        <v>13.202</v>
+        <v>3.609</v>
       </c>
       <c r="E108" s="1">
-        <v>13.202</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3188,16 +3230,16 @@
         <v>112</v>
       </c>
       <c r="B109" s="1">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="C109" s="1">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="D109" s="1">
-        <v>14.903</v>
+        <v>0.38</v>
       </c>
       <c r="E109" s="1">
-        <v>21.683</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3205,16 +3247,16 @@
         <v>113</v>
       </c>
       <c r="B110" s="1">
-        <v>0.4</v>
+        <v>0.112</v>
       </c>
       <c r="C110" s="1">
-        <v>0.61</v>
+        <v>0.152</v>
       </c>
       <c r="D110" s="1">
-        <v>8.016</v>
+        <v>0.396</v>
       </c>
       <c r="E110" s="1">
-        <v>15.815</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3222,16 +3264,16 @@
         <v>114</v>
       </c>
       <c r="B111" s="1">
-        <v>0.43</v>
+        <v>0.12</v>
       </c>
       <c r="C111" s="1">
-        <v>0.58</v>
+        <v>0.164</v>
       </c>
       <c r="D111" s="1">
-        <v>33.229</v>
+        <v>0.912</v>
       </c>
       <c r="E111" s="1">
-        <v>44.183</v>
+        <v>1.544</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3239,16 +3281,254 @@
         <v>115</v>
       </c>
       <c r="B112" s="1">
-        <v>0.52</v>
+        <v>0.116</v>
       </c>
       <c r="C112" s="1">
-        <v>0.72</v>
+        <v>0.14</v>
       </c>
       <c r="D112" s="1">
-        <v>26.113</v>
+        <v>0.4</v>
       </c>
       <c r="E112" s="1">
-        <v>36.257</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113" s="1">
+        <v>0.128</v>
+      </c>
+      <c r="C113" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="D113" s="1">
+        <v>3.84</v>
+      </c>
+      <c r="E113" s="1">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C114" s="1">
+        <v>0.144</v>
+      </c>
+      <c r="D114" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="E114" s="1">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C115" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="D115" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0.56</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C116" s="1">
+        <v>0.288</v>
+      </c>
+      <c r="D116" s="1">
+        <v>5.96</v>
+      </c>
+      <c r="E116" s="1">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" s="1">
+        <v>0.55</v>
+      </c>
+      <c r="C117" s="1">
+        <v>0.58</v>
+      </c>
+      <c r="D117" s="1">
+        <v>29.24</v>
+      </c>
+      <c r="E117" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" s="1">
+        <v>0.096</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0.128</v>
+      </c>
+      <c r="D118" s="1">
+        <v>5.584</v>
+      </c>
+      <c r="E118" s="1">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C119" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D119" s="1">
+        <v>5.165</v>
+      </c>
+      <c r="E119" s="1">
+        <v>7.44</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B120" s="1">
+        <v>0.172</v>
+      </c>
+      <c r="C120" s="1">
+        <v>0.244</v>
+      </c>
+      <c r="D120" s="1">
+        <v>2.24</v>
+      </c>
+      <c r="E120" s="1">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="C121" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="D121" s="1">
+        <v>1.15</v>
+      </c>
+      <c r="E121" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122" s="1">
+        <v>0.228</v>
+      </c>
+      <c r="C122" s="1">
+        <v>0.328</v>
+      </c>
+      <c r="D122" s="1">
+        <v>9.8</v>
+      </c>
+      <c r="E122" s="1">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B123" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="D123" s="1">
+        <v>3.976</v>
+      </c>
+      <c r="E123" s="1">
+        <v>4.136</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B124" s="1">
+        <v>0.128</v>
+      </c>
+      <c r="C124" s="1">
+        <v>0.204</v>
+      </c>
+      <c r="D124" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E124" s="1">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0.56</v>
+      </c>
+      <c r="D125" s="1">
+        <v>10.417</v>
+      </c>
+      <c r="E125" s="1">
+        <v>14.148</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" s="1">
+        <v>0.14</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0.204</v>
+      </c>
+      <c r="D126" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="E126" s="1">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/egg_data.xlsx
+++ b/egg_data.xlsx
@@ -269,7 +269,7 @@
     <t>古钟蛇</t>
   </si>
   <si>
-    <t>矮脚虎熊</t>
+    <t>矮脚爬爬</t>
   </si>
   <si>
     <t>火尾瓦特</t>
@@ -429,14 +429,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -907,139 +900,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
